--- a/apip/hb_result/hb_result_d50.xlsx
+++ b/apip/hb_result/hb_result_d50.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\yn\optimization\apip\hb_result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7B8606D0-84CF-446E-9E34-7A3738768AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D48E98F-498B-480A-8031-0C0DBB0ED044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B8176AAB-15F2-49D4-950E-F4DC9A666D85}"/>
   </bookViews>
@@ -766,7 +766,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -774,7 +774,7 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -791,26 +791,16 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="38100" cap="rnd">
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
           <c:xVal>
             <c:numRef>
@@ -1436,7 +1426,7 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-8F70-4F88-B6BB-CF1576FFB901}"/>
